--- a/src/test/resources/data/MassaDados.xlsx
+++ b/src/test/resources/data/MassaDados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DEV\TREINAMENTO\src\test\resources\dados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D76439-CC9C-46F5-84F3-D5FA12FD50D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE83D683-EB20-4DE8-86E1-C71B1E89AB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="45" windowWidth="17715" windowHeight="10740" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="48">
   <si>
     <t>TAG</t>
   </si>
@@ -135,9 +135,6 @@
     <t>6000</t>
   </si>
   <si>
-    <t>27589316857</t>
-  </si>
-  <si>
     <t>77589316857</t>
   </si>
   <si>
@@ -178,6 +175,12 @@
   </si>
   <si>
     <t>78046552313</t>
+  </si>
+  <si>
+    <t>96539101910</t>
+  </si>
+  <si>
+    <t>Conductor1</t>
   </si>
 </sst>
 </file>
@@ -227,11 +230,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -593,298 +593,298 @@
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.140625" style="8" customWidth="1"/>
-    <col min="5" max="5" width="7.85546875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4">
+        <v>77589316857</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4">
+        <v>77589316857</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4">
+        <v>38627653933</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="4">
+        <v>77589316857</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="5">
-        <v>77589316857</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="5">
-        <v>77589316857</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="5">
-        <v>38627653933</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="5">
-        <v>77589316857</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -900,48 +900,48 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>27</v>
       </c>
     </row>

--- a/src/test/resources/data/MassaDados.xlsx
+++ b/src/test/resources/data/MassaDados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE83D683-EB20-4DE8-86E1-C71B1E89AB9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641F05E9-F7F2-49C0-8DF9-6A285EFF839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
   <si>
     <t>TAG</t>
   </si>
@@ -60,9 +60,6 @@
     <t>Login</t>
   </si>
   <si>
-    <t>CT-1002</t>
-  </si>
-  <si>
     <t>CT-1003</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>Pix com sucesso</t>
   </si>
   <si>
-    <t>123457</t>
-  </si>
-  <si>
     <t>Receber Pix com sucesso</t>
   </si>
   <si>
@@ -159,9 +153,6 @@
     <t>Validar tentar logar logar com CPF válido e Senha inválida</t>
   </si>
   <si>
-    <t>654987</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
@@ -174,13 +165,13 @@
     <t>USUARIO_SECUNDARIO</t>
   </si>
   <si>
-    <t>78046552313</t>
-  </si>
-  <si>
     <t>96539101910</t>
   </si>
   <si>
     <t>Conductor1</t>
+  </si>
+  <si>
+    <t>05214098707</t>
   </si>
 </sst>
 </file>
@@ -230,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -250,11 +241,18 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,9 +594,10 @@
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="7" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="7"/>
+    <col min="8" max="8" width="21.5703125" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -614,17 +613,17 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>44</v>
+      <c r="H1" s="10" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -635,256 +634,256 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2">
+      <c r="H2" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H3">
+        <v>31</v>
+      </c>
+      <c r="D3" s="8">
+        <v>95211155807</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4">
+        <v>33</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="4">
-        <v>77589316857</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5">
+        <v>14</v>
+      </c>
+      <c r="D5" s="8">
+        <v>56645905998</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4">
-        <v>77589316857</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6">
+        <v>15</v>
+      </c>
+      <c r="D6" s="8">
+        <v>33524839576</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="4">
-        <v>38627653933</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7">
+        <v>16</v>
+      </c>
+      <c r="D7" s="8">
+        <v>53469909768</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="8">
+        <v>12312676745</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="4">
-        <v>77589316857</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8">
+      <c r="G8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9">
+        <v>35</v>
+      </c>
+      <c r="D9" s="8">
+        <v>16991161802</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10">
+        <v>37</v>
+      </c>
+      <c r="D10" s="8">
+        <v>88259498049</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="7">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="8">
+        <v>91999221770</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>32</v>
+      <c r="F11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -916,33 +915,33 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/data/MassaDados.xlsx
+++ b/src/test/resources/data/MassaDados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641F05E9-F7F2-49C0-8DF9-6A285EFF839E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED498449-A9B2-4CFD-96D1-E5A1F981064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="22305" windowHeight="15585" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="53">
   <si>
     <t>TAG</t>
   </si>
@@ -153,9 +153,6 @@
     <t>Validar tentar logar logar com CPF válido e Senha inválida</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>CT-1006</t>
   </si>
   <si>
@@ -172,6 +169,33 @@
   </si>
   <si>
     <t>05214098707</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>56645905998</t>
+  </si>
+  <si>
+    <t>33524839576</t>
+  </si>
+  <si>
+    <t>53469909768</t>
+  </si>
+  <si>
+    <t>12312676745</t>
+  </si>
+  <si>
+    <t>16991161802</t>
+  </si>
+  <si>
+    <t>88259498049</t>
+  </si>
+  <si>
+    <t>91999221770</t>
+  </si>
+  <si>
+    <t>17257347530</t>
   </si>
 </sst>
 </file>
@@ -201,12 +225,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -221,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -238,14 +268,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -253,6 +276,12 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,16 +617,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3A74B6D-8FA4-4011-9C72-01FBA93CFAED}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="53.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="13.28515625" style="7" customWidth="1"/>
-    <col min="6" max="7" width="9.140625" style="7"/>
-    <col min="8" max="8" width="21.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -613,17 +641,17 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>41</v>
+      <c r="H1" s="7" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -636,19 +664,19 @@
       <c r="C2" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2">
         <v>0</v>
       </c>
     </row>
@@ -657,24 +685,24 @@
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="8">
-        <v>95211155807</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="D3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3">
         <v>0</v>
       </c>
     </row>
@@ -688,19 +716,19 @@
       <c r="C4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="E4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4">
         <v>0</v>
       </c>
     </row>
@@ -714,19 +742,19 @@
       <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="8">
-        <v>56645905998</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="11" t="s">
+      <c r="D5" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5">
         <v>0</v>
       </c>
     </row>
@@ -740,19 +768,19 @@
       <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="8">
-        <v>33524839576</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="11" t="s">
+      <c r="D6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="G6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6">
         <v>0</v>
       </c>
     </row>
@@ -766,19 +794,19 @@
       <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="8">
-        <v>53469909768</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F7" s="11" t="s">
+      <c r="D7" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
@@ -792,19 +820,19 @@
       <c r="C8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="8">
-        <v>12312676745</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="11" t="s">
+      <c r="D8" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="G8" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
@@ -818,19 +846,19 @@
       <c r="C9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="8">
-        <v>16991161802</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="7">
+      <c r="D9" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9">
         <v>0</v>
       </c>
     </row>
@@ -844,52 +872,75 @@
       <c r="C10" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="8">
-        <v>88259498049</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="7">
+      <c r="D10" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="8">
-        <v>91999221770</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G14" s="8" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G15" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="D2 D4:D11" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -923,13 +974,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>30</v>

--- a/src/test/resources/data/MassaDados.xlsx
+++ b/src/test/resources/data/MassaDados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\myGithub\javaMobileAppiumTests\src\test\resources\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED498449-A9B2-4CFD-96D1-E5A1F981064D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{529C4873-44F8-45E1-AB54-424015E5CEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="22305" windowHeight="15585" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BE8CC490-7143-461B-A081-5E1B4D404489}"/>
   </bookViews>
   <sheets>
     <sheet name="USUARIO" sheetId="1" r:id="rId1"/>
@@ -60,9 +60,6 @@
     <t>Login</t>
   </si>
   <si>
-    <t>CT-1003</t>
-  </si>
-  <si>
     <t>CT-2001</t>
   </si>
   <si>
@@ -168,9 +165,6 @@
     <t>Conductor1</t>
   </si>
   <si>
-    <t>05214098707</t>
-  </si>
-  <si>
     <t>Home</t>
   </si>
   <si>
@@ -196,6 +190,12 @@
   </si>
   <si>
     <t>17257347530</t>
+  </si>
+  <si>
+    <t>CT-2002</t>
+  </si>
+  <si>
+    <t>Sacar</t>
   </si>
 </sst>
 </file>
@@ -645,13 +645,13 @@
         <v>4</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -662,19 +662,19 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
         <v>41</v>
       </c>
-      <c r="E2" t="s">
-        <v>42</v>
-      </c>
       <c r="F2" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -682,25 +682,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -708,25 +708,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>52</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>43</v>
+        <v>32</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -734,25 +734,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -760,25 +760,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -786,25 +786,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -812,25 +812,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D8" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -838,25 +838,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -864,25 +864,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -890,48 +890,48 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G12" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G13" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G14" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G15" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -939,7 +939,7 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="D2 D4:D11" numberStoredAsText="1"/>
+    <ignoredError sqref="D2 D5:D11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -966,33 +966,33 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
